--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T13:20:53+00:00</t>
+    <t>2026-05-11T15:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T11:16:16+00:00</t>
+    <t>2026-06-01T11:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T17:37:50+00:00</t>
+    <t>2026-06-15T21:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-ElgaListEntryFlagCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
